--- a/artfynd/A 48705-2020 artfynd.xlsx
+++ b/artfynd/A 48705-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48705-2020 artfynd.xlsx
+++ b/artfynd/A 48705-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2790,862 +2790,6 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112606350</v>
-      </c>
-      <c r="B20" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>663412</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7139424</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112606357</v>
-      </c>
-      <c r="B21" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>663464</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7139527</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>112606352</v>
-      </c>
-      <c r="B22" t="n">
-        <v>78953</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>663435</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7139250</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>112606351</v>
-      </c>
-      <c r="B23" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>663406</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7139268</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>112606356</v>
-      </c>
-      <c r="B24" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>663453</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7139508</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>112606358</v>
-      </c>
-      <c r="B25" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>663470</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7139561</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>112606354</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>663537</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7139542</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>112606355</v>
-      </c>
-      <c r="B27" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Granträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>663536</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7139530</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
